--- a/website/examples/example_odk_dce.points.xlsx
+++ b/website/examples/example_odk_dce.points.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R1122643341384340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R7ee96867313b474c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R691f44a8784d4f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Reb1510fe60e843f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R3742a48e7b844118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R10393283419c4835"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -475,7 +475,7 @@
         <x:v>Launch Points</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Configure the task below, then launch ResearchOS.</x:v>
+        <x:v>Configure the task below, then launch MethodMesh.</x:v>
       </x:c>
       <x:c r="E3" s="11"/>
       <x:c r="F3" s="11"/>
@@ -484,7 +484,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='dce.points',input_points='100',input64_items='UHJldmVudGlvbgpUcmVhdG1lbnQKVHJhaW5pbmcKVHJhbnNwb3J0',input_seed='participant_001',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='dce.points',input_points='100',input64_items='UHJldmVudGlvbgpUcmVhdG1lbnQKVHJhaW5pbmcKVHJhbnNwb3J0',input_seed='participant_001',return_mode='flat')</x:v>
       </x:c>
       <x:c r="J3" s="11"/>
       <x:c r="K3" s="11"/>
@@ -494,10 +494,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D4" s="11"/>
       <x:c r="E4" s="11"/>
@@ -515,10 +515,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>researchos_method_id</x:v>
+        <x:v>methodmesh_method_id</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>ResearchOS method ID</x:v>
+        <x:v>MethodMesh method ID</x:v>
       </x:c>
       <x:c r="D5" s="11"/>
       <x:c r="E5" s="11"/>
@@ -536,10 +536,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D6" s="11"/>
       <x:c r="E6" s="11"/>
